--- a/human_validation/judge/kor/judge_D001_S003_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D001_S003_P001__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.2576</v>
+        <v>0.0303</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.5455</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.3333</v>
+        <v>0.0303</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
